--- a/Result/checksun_a/2025-11-06.xlsx
+++ b/Result/checksun_a/2025-11-06.xlsx
@@ -17889,7 +17889,7 @@
       </c>
       <c r="AQ45" t="inlineStr">
         <is>
-          <t>99.502</t>
+          <t>99.50200000000001</t>
         </is>
       </c>
       <c r="AR45" t="inlineStr">
@@ -54345,7 +54345,7 @@
       </c>
       <c r="AQ138" t="inlineStr">
         <is>
-          <t>90.528</t>
+          <t>90.52799999999999</t>
         </is>
       </c>
       <c r="AR138" t="inlineStr">
